--- a/AAII_Financials/Yearly/SKY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SKY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/SKY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SKY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>SKY</t>
   </si>
@@ -656,209 +656,222 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45017</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44653</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44289</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43918</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43554</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43190</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42886</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42521</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42155</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41790</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41425</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41060</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40694</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2024800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2606600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2207200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1420900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1369700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1360000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1064700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>236500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>211800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>187000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>153100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>177600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>182800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>162300</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1539000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1787900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1618100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1133200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1090800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1114700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>887600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>214500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>188500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>169900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>142000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>166100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>178000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>160500</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>485800</v>
+      </c>
+      <c r="E10" s="3">
         <v>818700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>589100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>287700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>279000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>245400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>177100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>17100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1800</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,8 +889,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,9 +934,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,27 +982,30 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-5900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>600</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1001,8 +1021,8 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1010,9 +1030,12 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1025,18 +1048,18 @@
       <c r="F15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3">
         <v>5400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>500</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1049,15 +1072,18 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1098,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1852900</v>
+      </c>
+      <c r="E17" s="3">
         <v>2088300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1874300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1306200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1283300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1389800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1010100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>236200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>209600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>190800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>160400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>188200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>202200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>189000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>171900</v>
+      </c>
+      <c r="E18" s="3">
         <v>518300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>332900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>114600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>86500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-29700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>54600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-19400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,32 +1214,33 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E20" s="3">
         <v>18900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-6200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1214,179 +1248,191 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>240400</v>
+      </c>
+      <c r="E21" s="3">
         <v>563900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>354600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>132900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>108200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-19900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>56500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3">
         <v>-8500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-17000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-23900</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E22" s="3">
         <v>3300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>300</v>
       </c>
       <c r="K22" s="3">
         <v>300</v>
       </c>
       <c r="L22" s="3">
+        <v>300</v>
+      </c>
+      <c r="M22" s="3">
         <v>400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>200900</v>
+      </c>
+      <c r="E23" s="3">
         <v>533900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>330400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>111400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>85100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-41300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>43100</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>1900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-19400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E24" s="3">
         <v>132100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>82400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>26500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>26900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>16900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>27300</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1405,9 +1451,12 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1499,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>153700</v>
+      </c>
+      <c r="E26" s="3">
         <v>401800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>248000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>84900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>58200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-58200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15800</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>1900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-19400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>146700</v>
+      </c>
+      <c r="E27" s="3">
         <v>401800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>248000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>84800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>58000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-58200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>15800</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
         <v>1900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-19400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,23 +1643,26 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
@@ -1613,26 +1674,29 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-200</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-6200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-4600</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1739,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,33 +1787,36 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-18900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>6200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -1754,65 +1824,71 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>146700</v>
+      </c>
+      <c r="E33" s="3">
         <v>401800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>248000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>84800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>58000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-58200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>15800</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-19400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1931,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>146700</v>
+      </c>
+      <c r="E35" s="3">
         <v>401800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>248000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>84800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>58000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-58200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>15800</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-19400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45017</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44653</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44289</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43918</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43554</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43190</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42886</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42521</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42155</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41790</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41425</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41060</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40694</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2055,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,53 +2075,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>495100</v>
+      </c>
+      <c r="E41" s="3">
         <v>747500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>435400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>262600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>209500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>126600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>113700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9700</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2070,197 +2160,212 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>4000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>17000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>35000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E43" s="3">
         <v>67300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>90500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>57500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>45700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>57600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>42000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11500</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>318700</v>
+      </c>
+      <c r="E44" s="3">
         <v>202200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>241300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>166100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>126400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>122600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>98000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>11400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8700</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E45" s="3">
         <v>26500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>17200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3500</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>918300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1043500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>782300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>499800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>398800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>318300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>263100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>37300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>35800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>31600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>41700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>41600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>51500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>68400</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2292,89 +2397,95 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="N47" s="3">
         <v>1600</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
+      <c r="O47" s="3">
+        <v>1600</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>329600</v>
+      </c>
+      <c r="E48" s="3">
         <v>207400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>144200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>126600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>124100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>108600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>68000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>11600</v>
       </c>
       <c r="L48" s="3">
         <v>11600</v>
       </c>
       <c r="M48" s="3">
+        <v>11600</v>
+      </c>
+      <c r="N48" s="3">
         <v>14000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>21200</v>
       </c>
       <c r="O48" s="3">
         <v>21200</v>
       </c>
       <c r="P48" s="3">
+        <v>21200</v>
+      </c>
+      <c r="Q48" s="3">
         <v>24800</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>434300</v>
+      </c>
+      <c r="E49" s="3">
         <v>241900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>243300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>250600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>216900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>222300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4700</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2387,15 +2498,18 @@
       <c r="N49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2552,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2600,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>241100</v>
+      </c>
+      <c r="E52" s="3">
         <v>69900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>65000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>40900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>41900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>50700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>59600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5900</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2696,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1923300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1562700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1234600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>917900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>781700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>700000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>395400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>55600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>55000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>50400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>65800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>67900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>78900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>99100</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2767,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,77 +2787,81 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E57" s="3">
         <v>44700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>92200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>57200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>38700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>43400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>36800</v>
-      </c>
-      <c r="J57" s="3">
-        <v>3900</v>
       </c>
       <c r="K57" s="3">
         <v>3900</v>
       </c>
       <c r="L57" s="3">
-        <v>3000</v>
+        <v>3900</v>
       </c>
       <c r="M57" s="3">
         <v>3000</v>
       </c>
       <c r="N57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O57" s="3">
         <v>3700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3400</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>91300</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>35500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>25700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>33900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>33300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>30200</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
       </c>
@@ -2740,128 +2874,137 @@
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>247500</v>
+      </c>
+      <c r="E59" s="3">
         <v>204200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>222500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>180700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>114000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>129600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>100100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11300</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>389600</v>
+      </c>
+      <c r="E60" s="3">
         <v>248900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>350100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>263600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>186600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>206300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>167100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14200</v>
-      </c>
-      <c r="O60" s="3">
-        <v>14700</v>
       </c>
       <c r="P60" s="3">
         <v>14700</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>14700</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>12400</v>
+        <v>24700</v>
       </c>
       <c r="E61" s="3">
         <v>12400</v>
       </c>
       <c r="F61" s="3">
+        <v>12400</v>
+      </c>
+      <c r="G61" s="3">
         <v>39300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>77300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>54300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>58900</v>
-      </c>
-      <c r="J61" s="3">
-        <v>4300</v>
       </c>
       <c r="K61" s="3">
         <v>4300</v>
@@ -2870,65 +3013,71 @@
         <v>4300</v>
       </c>
       <c r="M61" s="3">
+        <v>4300</v>
+      </c>
+      <c r="N61" s="3">
         <v>6300</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>86700</v>
+      </c>
+      <c r="E62" s="3">
         <v>68400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>47000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>46300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>43400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>27300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7300</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3120,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3168,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3216,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>501000</v>
+      </c>
+      <c r="E66" s="3">
         <v>329700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>409500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>349300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>307400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>288000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>242100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>29800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>22300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22100</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3287,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3332,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3380,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3428,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3476,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>866500</v>
+      </c>
+      <c r="E72" s="3">
         <v>725700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>327900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>82900</v>
       </c>
-      <c r="G72" s="3">
-        <v>0</v>
-      </c>
       <c r="H72" s="3">
+        <v>0</v>
+      </c>
+      <c r="I72" s="3">
         <v>-58200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>22500</v>
-      </c>
-      <c r="J72" s="3">
-        <v>85600</v>
       </c>
       <c r="K72" s="3">
         <v>85600</v>
       </c>
       <c r="L72" s="3">
+        <v>85600</v>
+      </c>
+      <c r="M72" s="3">
         <v>83900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>94300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>106200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>116700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>137500</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3572,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3620,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3668,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1422400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1233000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>825100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>568600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>474300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>412000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>153300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>33800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>45700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>56200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>77000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3764,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45017</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44653</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44289</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43918</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43554</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43190</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42886</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42521</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42155</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41790</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41425</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41060</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40694</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>146700</v>
+      </c>
+      <c r="E81" s="3">
         <v>401800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>248000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>84800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>58000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-58200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>15800</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
         <v>1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-19400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3888,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E83" s="3">
         <v>26700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>20900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>18500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>2000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2700</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3981,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4029,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4077,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4125,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4173,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>222700</v>
+      </c>
+      <c r="E89" s="3">
         <v>416200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>224500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>153900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>76700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>65200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>31600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-17600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-18600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-25600</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4244,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-52900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-52200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-32000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4337,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4385,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-485700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-61200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-32000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-56800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>5600</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>13900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>22400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>32100</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,8 +4456,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4241,14 +4475,14 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>-65300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-900</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -4262,14 +4496,17 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-1500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4549,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4597,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,78 +4645,84 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-37000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-19900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-47800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>21600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-72500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>10300</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-2300</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-1500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
@@ -4486,58 +4735,64 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-252400</v>
+      </c>
+      <c r="E102" s="3">
         <v>312000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>172800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>53100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>82800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>33900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>500</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SKY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SKY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>SKY</t>
   </si>
@@ -994,23 +994,23 @@
       <c r="D14" s="3">
         <v>3300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-5900</v>
+      <c r="E14" s="3">
+        <v>300</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3">
-        <v>600</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+        <v>2500</v>
+      </c>
+      <c r="I14" s="3">
+        <v>17900</v>
+      </c>
+      <c r="J14" s="3">
+        <v>7700</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1039,23 +1039,23 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>8</v>
+      <c r="D15" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E15" s="3">
+        <v>26700</v>
+      </c>
+      <c r="F15" s="3">
+        <v>20900</v>
+      </c>
+      <c r="G15" s="3">
+        <v>17700</v>
       </c>
       <c r="H15" s="3">
-        <v>5400</v>
+        <v>18500</v>
       </c>
       <c r="I15" s="3">
-        <v>4800</v>
+        <v>16100</v>
       </c>
       <c r="J15" s="3">
         <v>500</v>
@@ -1105,7 +1105,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1852900</v>
+        <v>1849600</v>
       </c>
       <c r="E17" s="3">
         <v>2088300</v>
@@ -1114,16 +1114,16 @@
         <v>1874300</v>
       </c>
       <c r="G17" s="3">
-        <v>1306200</v>
+        <v>1312100</v>
       </c>
       <c r="H17" s="3">
-        <v>1283300</v>
+        <v>1280700</v>
       </c>
       <c r="I17" s="3">
-        <v>1389800</v>
+        <v>1380200</v>
       </c>
       <c r="J17" s="3">
-        <v>1010100</v>
+        <v>1010300</v>
       </c>
       <c r="K17" s="3">
         <v>236200</v>
@@ -1153,7 +1153,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>171900</v>
+        <v>175200</v>
       </c>
       <c r="E18" s="3">
         <v>518300</v>
@@ -1162,16 +1162,16 @@
         <v>332900</v>
       </c>
       <c r="G18" s="3">
-        <v>114600</v>
+        <v>108800</v>
       </c>
       <c r="H18" s="3">
-        <v>86500</v>
+        <v>89000</v>
       </c>
       <c r="I18" s="3">
-        <v>-29700</v>
+        <v>-20100</v>
       </c>
       <c r="J18" s="3">
-        <v>54600</v>
+        <v>54400</v>
       </c>
       <c r="K18" s="3">
         <v>300</v>
@@ -1221,25 +1221,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>33600</v>
+        <v>7000</v>
       </c>
       <c r="E20" s="3">
-        <v>18900</v>
+        <v>-1000</v>
       </c>
       <c r="F20" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>3200</v>
+        <v>-5900</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I20" s="3">
-        <v>-6200</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>-6300</v>
+        <v>-500</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1269,25 +1269,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>240400</v>
+        <v>203100</v>
       </c>
       <c r="E21" s="3">
-        <v>563900</v>
+        <v>546000</v>
       </c>
       <c r="F21" s="3">
-        <v>354600</v>
+        <v>353900</v>
       </c>
       <c r="G21" s="3">
-        <v>132900</v>
+        <v>132400</v>
       </c>
       <c r="H21" s="3">
-        <v>108200</v>
+        <v>107500</v>
       </c>
       <c r="I21" s="3">
-        <v>-19900</v>
+        <v>-4000</v>
       </c>
       <c r="J21" s="3">
-        <v>56500</v>
+        <v>55500</v>
       </c>
       <c r="K21" s="3">
         <v>1400</v>
@@ -1365,7 +1365,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>200900</v>
+        <v>193800</v>
       </c>
       <c r="E23" s="3">
         <v>533900</v>
@@ -1509,7 +1509,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>153700</v>
+        <v>146700</v>
       </c>
       <c r="E26" s="3">
         <v>401800</v>
@@ -1575,7 +1575,7 @@
         <v>-58200</v>
       </c>
       <c r="J27" s="3">
-        <v>15800</v>
+        <v>14800</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -1797,25 +1797,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-33600</v>
+        <v>-7000</v>
       </c>
       <c r="E32" s="3">
-        <v>-18900</v>
+        <v>1000</v>
       </c>
       <c r="F32" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-3200</v>
+        <v>5900</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I32" s="3">
-        <v>6200</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>6300</v>
+        <v>500</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>248000</v>
       </c>
       <c r="G33" s="3">
-        <v>84800</v>
+        <v>84900</v>
       </c>
       <c r="H33" s="3">
-        <v>58000</v>
+        <v>58200</v>
       </c>
       <c r="I33" s="3">
         <v>-58200</v>
@@ -1950,10 +1950,10 @@
         <v>248000</v>
       </c>
       <c r="G35" s="3">
-        <v>84800</v>
+        <v>84900</v>
       </c>
       <c r="H35" s="3">
-        <v>58000</v>
+        <v>58200</v>
       </c>
       <c r="I35" s="3">
         <v>-58200</v>
@@ -2370,25 +2370,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>136400</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2610,25 +2610,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>241100</v>
+        <v>52100</v>
       </c>
       <c r="E52" s="3">
-        <v>69900</v>
+        <v>27500</v>
       </c>
       <c r="F52" s="3">
-        <v>65000</v>
+        <v>26700</v>
       </c>
       <c r="G52" s="3">
-        <v>40900</v>
+        <v>20700</v>
       </c>
       <c r="H52" s="3">
-        <v>41900</v>
+        <v>20100</v>
       </c>
       <c r="I52" s="3">
-        <v>50700</v>
+        <v>16700</v>
       </c>
       <c r="J52" s="3">
-        <v>59600</v>
+        <v>29300</v>
       </c>
       <c r="K52" s="3">
         <v>7400</v>
@@ -2842,19 +2842,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>91300</v>
+        <v>98800</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="F58" s="3">
-        <v>35500</v>
+        <v>40100</v>
       </c>
       <c r="G58" s="3">
-        <v>25700</v>
+        <v>30000</v>
       </c>
       <c r="H58" s="3">
-        <v>33900</v>
+        <v>38700</v>
       </c>
       <c r="I58" s="3">
         <v>33300</v>
@@ -2890,25 +2890,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>247500</v>
+        <v>136500</v>
       </c>
       <c r="E59" s="3">
-        <v>204200</v>
+        <v>115700</v>
       </c>
       <c r="F59" s="3">
-        <v>222500</v>
+        <v>115900</v>
       </c>
       <c r="G59" s="3">
-        <v>180700</v>
+        <v>103300</v>
       </c>
       <c r="H59" s="3">
-        <v>114000</v>
+        <v>52800</v>
       </c>
       <c r="I59" s="3">
-        <v>129600</v>
+        <v>60200</v>
       </c>
       <c r="J59" s="3">
-        <v>100100</v>
+        <v>47900</v>
       </c>
       <c r="K59" s="3">
         <v>14500</v>
@@ -2986,19 +2986,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>24700</v>
+        <v>55900</v>
       </c>
       <c r="E61" s="3">
-        <v>12400</v>
+        <v>35800</v>
       </c>
       <c r="F61" s="3">
-        <v>12400</v>
+        <v>19000</v>
       </c>
       <c r="G61" s="3">
-        <v>39300</v>
+        <v>46600</v>
       </c>
       <c r="H61" s="3">
-        <v>77300</v>
+        <v>87300</v>
       </c>
       <c r="I61" s="3">
         <v>54300</v>
@@ -3034,25 +3034,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>86700</v>
+        <v>48500</v>
       </c>
       <c r="E62" s="3">
-        <v>68400</v>
+        <v>39000</v>
       </c>
       <c r="F62" s="3">
-        <v>47000</v>
+        <v>35300</v>
       </c>
       <c r="G62" s="3">
-        <v>46300</v>
+        <v>34800</v>
       </c>
       <c r="H62" s="3">
-        <v>43400</v>
+        <v>30100</v>
       </c>
       <c r="I62" s="3">
-        <v>27300</v>
+        <v>23900</v>
       </c>
       <c r="J62" s="3">
-        <v>16100</v>
+        <v>12800</v>
       </c>
       <c r="K62" s="3">
         <v>7600</v>
@@ -3836,10 +3836,10 @@
         <v>248000</v>
       </c>
       <c r="G81" s="3">
-        <v>84800</v>
+        <v>84900</v>
       </c>
       <c r="H81" s="3">
-        <v>58000</v>
+        <v>58200</v>
       </c>
       <c r="I81" s="3">
         <v>-58200</v>
@@ -3895,25 +3895,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>34900</v>
+        <v>24100</v>
       </c>
       <c r="E83" s="3">
-        <v>26700</v>
+        <v>16100</v>
       </c>
       <c r="F83" s="3">
-        <v>20900</v>
+        <v>13400</v>
       </c>
       <c r="G83" s="3">
-        <v>17700</v>
+        <v>12100</v>
       </c>
       <c r="H83" s="3">
-        <v>18500</v>
+        <v>13100</v>
       </c>
       <c r="I83" s="3">
-        <v>16100</v>
+        <v>11300</v>
       </c>
       <c r="J83" s="3">
-        <v>8300</v>
+        <v>7800</v>
       </c>
       <c r="K83" s="3">
         <v>1000</v>
@@ -4478,10 +4478,10 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-65300</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/SKY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SKY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
   <si>
     <t>SKY</t>
   </si>
@@ -656,222 +656,234 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45017</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44653</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44289</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43918</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43554</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42886</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42521</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42155</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41790</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41425</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41060</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40694</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2483400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2024800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2606600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2207200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1420900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1369700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1360000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1064700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>236500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>211800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>187000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>153100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>177600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>182800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>162300</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1819400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1539000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1787900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1618100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1133200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1090800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1114700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>887600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>214500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>188500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>169900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>142000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>166100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>178000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>160500</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>664000</v>
+      </c>
+      <c r="E10" s="3">
         <v>485800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>818700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>589100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>287700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>279000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>245400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>177100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>22000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>23300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>17100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1800</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -890,8 +902,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -937,9 +950,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,36 +1001,39 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E14" s="3">
         <v>3300</v>
       </c>
-      <c r="E14" s="3">
-        <v>300</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>2500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>17900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1024,8 +1043,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1033,36 +1052,39 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E15" s="3">
         <v>34900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>26700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>17700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>18500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>16100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>500</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1075,15 +1097,18 @@
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1099,104 +1124,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2237800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1849600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2088300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1874300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1312100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1280700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1380200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1010300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>236200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>209600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>190800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>160400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>188200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>202200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>189000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>245700</v>
+      </c>
+      <c r="E18" s="3">
         <v>175200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>518300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>332900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>108800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>89000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-20100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>54400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-10600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-26700</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1215,35 +1247,36 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>7000</v>
       </c>
-      <c r="E20" s="3">
-        <v>-1000</v>
-      </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-5900</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1251,191 +1284,203 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>285500</v>
+      </c>
+      <c r="E21" s="3">
         <v>203100</v>
       </c>
-      <c r="E21" s="3">
-        <v>546000</v>
-      </c>
       <c r="F21" s="3">
+        <v>545600</v>
+      </c>
+      <c r="G21" s="3">
         <v>353900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>132400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>107500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>55500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2500</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>-8500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-23900</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E22" s="3">
         <v>4600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>300</v>
       </c>
       <c r="L22" s="3">
         <v>300</v>
       </c>
       <c r="M22" s="3">
+        <v>300</v>
+      </c>
+      <c r="N22" s="3">
         <v>400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>255400</v>
+      </c>
+      <c r="E23" s="3">
         <v>193800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>533900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>330400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>111400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>85100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-41300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>43100</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
       <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>1900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-26600</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E24" s="3">
         <v>47100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>132100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>82400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>26500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>26900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>16900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>27300</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -1454,9 +1499,12 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1502,105 +1550,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>201600</v>
+      </c>
+      <c r="E26" s="3">
         <v>146700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>401800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>248000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>84900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>58200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-58200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15800</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
       <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>1900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-26600</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>198400</v>
+      </c>
+      <c r="E27" s="3">
         <v>146700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>401800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>248000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>84800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>58000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-58200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>14800</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
       <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>1900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-26600</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1646,9 +1703,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,26 +1737,29 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-6200</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-4600</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1742,9 +1805,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1790,36 +1856,39 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7000</v>
       </c>
-      <c r="E32" s="3">
-        <v>1000</v>
-      </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>5900</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -1827,68 +1896,74 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>198400</v>
+      </c>
+      <c r="E33" s="3">
         <v>146700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>401800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>248000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>84900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>58200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-58200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15800</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
       <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
         <v>1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-11900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-26600</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1934,110 +2009,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>198400</v>
+      </c>
+      <c r="E35" s="3">
         <v>146700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>401800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>248000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>84900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>58200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-58200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15800</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
       <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-11900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-26600</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45017</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44653</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44289</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43918</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43554</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42886</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42521</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42155</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41790</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41425</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41060</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40694</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2056,8 +2140,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2076,56 +2161,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>610300</v>
+      </c>
+      <c r="E41" s="3">
         <v>495100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>747500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>435400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>262600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>209500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>126600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>113700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9700</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2163,218 +2252,233 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>4000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>17000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>35000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>84100</v>
+      </c>
+      <c r="E43" s="3">
         <v>64600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>67300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>90500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>57500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>45700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>57600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>42000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11500</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>360600</v>
+      </c>
+      <c r="E44" s="3">
         <v>318700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>202200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>241300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>166100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>126400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>122600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>98000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>11400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8700</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E45" s="3">
         <v>39900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>26500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>17200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3500</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1086500</v>
+      </c>
+      <c r="E46" s="3">
         <v>918300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1043500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>782300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>499800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>398800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>318300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>263100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>37300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>35800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>31600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>41700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>41600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>51500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>68400</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>134700</v>
+      </c>
+      <c r="E47" s="3">
         <v>136400</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2390,8 +2494,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2400,95 +2504,101 @@
         <v>0</v>
       </c>
       <c r="N47" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="O47" s="3">
         <v>1600</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>8</v>
+      <c r="P47" s="3">
+        <v>1600</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>339500</v>
+      </c>
+      <c r="E48" s="3">
         <v>329600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>207400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>144200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>126600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>124100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>108600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>68000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>11600</v>
       </c>
       <c r="M48" s="3">
         <v>11600</v>
       </c>
       <c r="N48" s="3">
+        <v>11600</v>
+      </c>
+      <c r="O48" s="3">
         <v>14000</v>
-      </c>
-      <c r="O48" s="3">
-        <v>21200</v>
       </c>
       <c r="P48" s="3">
         <v>21200</v>
       </c>
       <c r="Q48" s="3">
+        <v>21200</v>
+      </c>
+      <c r="R48" s="3">
         <v>24800</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>422700</v>
+      </c>
+      <c r="E49" s="3">
         <v>434300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>241900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>243300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>250600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>216900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>222300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4700</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2501,15 +2611,18 @@
       <c r="O49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2555,9 +2668,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2603,57 +2719,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E52" s="3">
         <v>52100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>26700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>20700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>29300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5900</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2699,57 +2821,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2110400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1923300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1562700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1234600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>917900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>781700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>700000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>395400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>55600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>55000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>50400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>65800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>67900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>78900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>99100</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2768,8 +2896,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2788,83 +2917,87 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E57" s="3">
         <v>50800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>44700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>92200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>57200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>38700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>43400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>36800</v>
-      </c>
-      <c r="K57" s="3">
-        <v>3900</v>
       </c>
       <c r="L57" s="3">
         <v>3900</v>
       </c>
       <c r="M57" s="3">
-        <v>3000</v>
+        <v>3900</v>
       </c>
       <c r="N57" s="3">
         <v>3000</v>
       </c>
       <c r="O57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P57" s="3">
         <v>3700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3400</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>115400</v>
+      </c>
+      <c r="E58" s="3">
         <v>98800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>40100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>30000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>38700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>33300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>30200</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>8</v>
       </c>
@@ -2877,137 +3010,146 @@
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E59" s="3">
         <v>136500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>115700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>115900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>103300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>52800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>60200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>47900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11300</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>451300</v>
+      </c>
+      <c r="E60" s="3">
         <v>389600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>248900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>350100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>263600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>186600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>206300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>167100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14200</v>
-      </c>
-      <c r="P60" s="3">
-        <v>14700</v>
       </c>
       <c r="Q60" s="3">
         <v>14700</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>14700</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E61" s="3">
         <v>55900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>35800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>46600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>87300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>54300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>58900</v>
-      </c>
-      <c r="K61" s="3">
-        <v>4300</v>
       </c>
       <c r="L61" s="3">
         <v>4300</v>
@@ -3016,68 +3158,74 @@
         <v>4300</v>
       </c>
       <c r="N61" s="3">
+        <v>4300</v>
+      </c>
+      <c r="O61" s="3">
         <v>6300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E62" s="3">
         <v>48500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>39000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>35300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>34800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>30100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>23900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7300</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3123,9 +3271,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3171,9 +3322,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3219,57 +3373,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>566000</v>
+      </c>
+      <c r="E66" s="3">
         <v>501000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>329700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>409500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>349300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>307400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>288000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>242100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>30300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>29800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>27100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>32000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22100</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3288,8 +3448,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3335,9 +3496,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3383,9 +3547,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3431,9 +3598,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3479,57 +3649,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>976000</v>
+      </c>
+      <c r="E72" s="3">
         <v>866500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>725700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>327900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>82900</v>
       </c>
-      <c r="H72" s="3">
-        <v>0</v>
-      </c>
       <c r="I72" s="3">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3">
         <v>-58200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>22500</v>
-      </c>
-      <c r="K72" s="3">
-        <v>85600</v>
       </c>
       <c r="L72" s="3">
         <v>85600</v>
       </c>
       <c r="M72" s="3">
+        <v>85600</v>
+      </c>
+      <c r="N72" s="3">
         <v>83900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>94300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>106200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>116700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>137500</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3575,9 +3751,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3623,9 +3802,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3671,57 +3853,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1544400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1422400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1233000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>825100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>568600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>474300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>412000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>153300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>33800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>45700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>56200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>77000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3767,110 +3955,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45017</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44653</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44289</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43918</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43554</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42886</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42521</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42155</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41790</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41425</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41060</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40694</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>198400</v>
+      </c>
+      <c r="E81" s="3">
         <v>146700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>401800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>248000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>84900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>58200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-58200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15800</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
       <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
         <v>1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-11900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-26600</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3889,56 +4086,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E83" s="3">
         <v>24100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>13400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>11300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1300</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3">
         <v>2000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2700</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3984,9 +4185,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4032,9 +4236,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4080,9 +4287,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4128,9 +4338,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4176,57 +4389,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>240900</v>
+      </c>
+      <c r="E89" s="3">
         <v>222700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>416200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>224500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>153900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>76700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>65200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>31600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-17600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-14000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-25600</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4245,56 +4464,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-50500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-52900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-52200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-32000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4340,9 +4563,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4388,57 +4614,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-46200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-485700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-61200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-32000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-56800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>5600</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3">
         <v>13900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>22400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>32100</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4457,8 +4689,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4499,14 +4732,17 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-6000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4552,9 +4788,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4600,9 +4839,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4648,84 +4890,90 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="E100" s="3">
         <v>10900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-37000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-19900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-47800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>21600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-72500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>10300</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-2300</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-6000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
@@ -4738,61 +4986,67 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>115300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-252400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>312000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>172800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>53100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>82800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>33900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>500</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SKY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SKY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>SKY</t>
   </si>
@@ -656,234 +656,246 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44653</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44289</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43918</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43554</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42886</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42521</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42155</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41790</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41425</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>41060</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>40694</v>
       </c>
-      <c r="S7" s="2"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2663600</v>
+      </c>
+      <c r="E8" s="3">
         <v>2483400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2024800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2606600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2207200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1420900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1369700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1360000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1064700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>236500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>211800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>187000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>153100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>177600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>182800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>162300</v>
       </c>
-      <c r="S8" s="3"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1959300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1819400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1539000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1787900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1618100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1133200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1090800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1114700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>887600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>214500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>188500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>169900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>142000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>166100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>178000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>160500</v>
       </c>
-      <c r="S9" s="3"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>704300</v>
+      </c>
+      <c r="E10" s="3">
         <v>664000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>485800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>818700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>589100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>287700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>279000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>245400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>177100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>22000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>23300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>17100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1800</v>
       </c>
-      <c r="S10" s="3"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -903,8 +915,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -953,9 +966,12 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S12" s="3"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,18 +1020,21 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-      <c r="S13" s="3"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E14" s="3">
         <v>7600</v>
       </c>
-      <c r="E14" s="3">
-        <v>3300</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1025,18 +1044,18 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>2500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>17900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1046,8 +1065,8 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1055,39 +1074,42 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E15" s="3">
         <v>41900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>34900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>26700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>20900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>18500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>16100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>500</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1100,15 +1122,18 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1125,110 +1150,117 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2405200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2237800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1849600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2088300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1874300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1312100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1280700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1380200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1010300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>236200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>209600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>190800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>160400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>188200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>202200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>189000</v>
       </c>
-      <c r="S17" s="3"/>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>258400</v>
+      </c>
+      <c r="E18" s="3">
         <v>245700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>175200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>518300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>332900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>108800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>89000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-20100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>54400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-19400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-26700</v>
       </c>
-      <c r="S18" s="3"/>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1248,38 +1280,39 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
         <v>2000</v>
       </c>
-      <c r="E20" s="3">
-        <v>7000</v>
-      </c>
       <c r="F20" s="3">
+        <v>9600</v>
+      </c>
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-5900</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1287,203 +1320,215 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3"/>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>306600</v>
+      </c>
+      <c r="E21" s="3">
         <v>285500</v>
       </c>
-      <c r="E21" s="3">
-        <v>203100</v>
-      </c>
       <c r="F21" s="3">
+        <v>200500</v>
+      </c>
+      <c r="G21" s="3">
         <v>545600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>353900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>132400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>107500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>55500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-17000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-23900</v>
       </c>
-      <c r="S21" s="3"/>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E22" s="3">
         <v>8500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>300</v>
       </c>
       <c r="M22" s="3">
         <v>300</v>
       </c>
       <c r="N22" s="3">
+        <v>300</v>
+      </c>
+      <c r="O22" s="3">
         <v>400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S22" s="3"/>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>271000</v>
+      </c>
+      <c r="E23" s="3">
         <v>255400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>193800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>533900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>330400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>111400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>85100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-41300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>43100</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
       <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>1900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-19400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-26600</v>
       </c>
-      <c r="S23" s="3"/>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3"/>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E24" s="3">
         <v>53700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>47100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>132100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>82400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>26500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>26900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>16900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>27300</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1502,9 +1547,12 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3"/>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3"/>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1553,111 +1601,120 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-      <c r="S25" s="3"/>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3"/>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>214200</v>
+      </c>
+      <c r="E26" s="3">
         <v>201600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>146700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>401800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>248000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>84900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>58200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-58200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15800</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
       <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>1900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-19400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-26600</v>
       </c>
-      <c r="S26" s="3"/>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3"/>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>206900</v>
+      </c>
+      <c r="E27" s="3">
         <v>198400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>146700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>401800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>248000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>84800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>58000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-58200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14800</v>
       </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
       <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>1900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-19400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-26600</v>
       </c>
-      <c r="S27" s="3"/>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3"/>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1706,9 +1763,12 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-      <c r="S28" s="3"/>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3"/>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1740,26 +1800,29 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-200</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-6200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-4600</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3"/>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3"/>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1808,9 +1871,12 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-      <c r="S30" s="3"/>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3"/>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1859,39 +1925,42 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-      <c r="S31" s="3"/>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3"/>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2000</v>
       </c>
-      <c r="E32" s="3">
-        <v>-7000</v>
-      </c>
       <c r="F32" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>5900</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -1899,71 +1968,77 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3"/>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3"/>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>206900</v>
+      </c>
+      <c r="E33" s="3">
         <v>198400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>146700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>401800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>248000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>84900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>58200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-58200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>15800</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
       <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>1700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-11900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-19400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-26600</v>
       </c>
-      <c r="S33" s="3"/>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3"/>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2012,116 +2087,125 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-      <c r="S34" s="3"/>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3"/>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>206900</v>
+      </c>
+      <c r="E35" s="3">
         <v>198400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>146700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>401800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>248000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>84900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>58200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-58200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>15800</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
       <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>1700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-11900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-19400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-26600</v>
       </c>
-      <c r="S35" s="3"/>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3"/>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44653</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44289</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43918</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43554</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42886</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42521</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42155</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41790</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41425</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>41060</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>40694</v>
       </c>
-      <c r="S38" s="2"/>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2"/>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2141,8 +2225,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2162,59 +2247,63 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>638300</v>
+      </c>
+      <c r="E41" s="3">
         <v>610300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>495100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>747500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>435400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>262600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>209500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>126600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>113700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9700</v>
       </c>
-      <c r="S41" s="3"/>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3"/>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2255,233 +2344,248 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>4000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>17000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>35000</v>
       </c>
-      <c r="S42" s="3"/>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3"/>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>88800</v>
+      </c>
+      <c r="E43" s="3">
         <v>84100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>64600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>67300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>90500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>57500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>45700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>57600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>42000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11500</v>
       </c>
-      <c r="S43" s="3"/>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3"/>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>358300</v>
+      </c>
+      <c r="E44" s="3">
         <v>360600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>318700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>202200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>241300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>166100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>126400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>122600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>98000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>11400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>9100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8700</v>
       </c>
-      <c r="S44" s="3"/>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3"/>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E45" s="3">
         <v>31400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>39900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>26500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>15000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>17200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3500</v>
       </c>
-      <c r="S45" s="3"/>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3"/>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1128200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1086500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>918300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1043500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>782300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>499800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>398800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>318300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>263100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>37300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>35800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>31600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>41700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>41600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>51500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>68400</v>
       </c>
-      <c r="S46" s="3"/>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3"/>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E47" s="3">
         <v>134700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>136400</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2497,8 +2601,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2507,101 +2611,107 @@
         <v>0</v>
       </c>
       <c r="O47" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="P47" s="3">
         <v>1600</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
+      <c r="Q47" s="3">
+        <v>1600</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3"/>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T47" s="3"/>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>341200</v>
+      </c>
+      <c r="E48" s="3">
         <v>339500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>329600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>207400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>144200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>126600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>124100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>108600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>68000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>11600</v>
       </c>
       <c r="N48" s="3">
         <v>11600</v>
       </c>
       <c r="O48" s="3">
+        <v>11600</v>
+      </c>
+      <c r="P48" s="3">
         <v>14000</v>
-      </c>
-      <c r="P48" s="3">
-        <v>21200</v>
       </c>
       <c r="Q48" s="3">
         <v>21200</v>
       </c>
       <c r="R48" s="3">
+        <v>21200</v>
+      </c>
+      <c r="S48" s="3">
         <v>24800</v>
       </c>
-      <c r="S48" s="3"/>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3"/>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>421000</v>
+      </c>
+      <c r="E49" s="3">
         <v>422700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>434300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>241900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>243300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>250600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>216900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>222300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4700</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2614,15 +2724,18 @@
       <c r="P49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
-      <c r="S49" s="3"/>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3"/>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2671,9 +2784,12 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-      <c r="S50" s="3"/>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3"/>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2722,60 +2838,66 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-      <c r="S51" s="3"/>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3"/>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>63300</v>
+      </c>
+      <c r="E52" s="3">
         <v>66000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>52100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>26700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>29300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5900</v>
       </c>
-      <c r="S52" s="3"/>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3"/>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2824,60 +2946,66 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-      <c r="S53" s="3"/>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3"/>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2131500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2110400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1923300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1562700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1234600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>917900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>781700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>700000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>395400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>55600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>55000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>50400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>65800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>67900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>78900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>99100</v>
       </c>
-      <c r="S54" s="3"/>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3"/>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2897,8 +3025,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2918,89 +3047,93 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E57" s="3">
         <v>65100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>50800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>44700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>92200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>57200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>38700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>43400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>36800</v>
-      </c>
-      <c r="L57" s="3">
-        <v>3900</v>
       </c>
       <c r="M57" s="3">
         <v>3900</v>
       </c>
       <c r="N57" s="3">
-        <v>3000</v>
+        <v>3900</v>
       </c>
       <c r="O57" s="3">
         <v>3000</v>
       </c>
       <c r="P57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Q57" s="3">
         <v>3700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3400</v>
       </c>
-      <c r="S57" s="3"/>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3"/>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>112800</v>
+      </c>
+      <c r="E58" s="3">
         <v>115400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>98800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>40100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>30000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>38700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>33300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>30200</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3013,146 +3146,155 @@
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3"/>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3"/>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>139400</v>
+      </c>
+      <c r="E59" s="3">
         <v>142000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>136500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>115700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>115900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>103300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>52800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>60200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>47900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11300</v>
       </c>
-      <c r="S59" s="3"/>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3"/>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>455300</v>
+      </c>
+      <c r="E60" s="3">
         <v>451300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>389600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>248900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>350100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>263600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>186600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>206300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>167100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>15100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14200</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>14700</v>
       </c>
       <c r="R60" s="3">
         <v>14700</v>
       </c>
-      <c r="S60" s="3"/>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>14700</v>
+      </c>
+      <c r="T60" s="3"/>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E61" s="3">
         <v>48400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>55900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>35800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>19000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>46600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>87300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>54300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>58900</v>
-      </c>
-      <c r="L61" s="3">
-        <v>4300</v>
       </c>
       <c r="M61" s="3">
         <v>4300</v>
@@ -3161,71 +3303,77 @@
         <v>4300</v>
       </c>
       <c r="O61" s="3">
+        <v>4300</v>
+      </c>
+      <c r="P61" s="3">
         <v>6300</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
-      <c r="S61" s="3"/>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3"/>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E62" s="3">
         <v>58900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>48500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>39000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>35300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>34800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>30100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>23900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7300</v>
       </c>
-      <c r="S62" s="3"/>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3"/>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3274,9 +3422,12 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-      <c r="S63" s="3"/>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3"/>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3325,9 +3476,12 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-      <c r="S64" s="3"/>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3"/>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3376,60 +3530,66 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-      <c r="S65" s="3"/>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3"/>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>558600</v>
+      </c>
+      <c r="E66" s="3">
         <v>566000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>501000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>329700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>409500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>349300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>307400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>288000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>242100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>30300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>29800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>32000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>22100</v>
       </c>
-      <c r="S66" s="3"/>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3"/>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3449,8 +3609,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3499,9 +3660,12 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-      <c r="S68" s="3"/>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3"/>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3550,9 +3714,12 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-      <c r="S69" s="3"/>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3"/>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3601,9 +3768,12 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-      <c r="S70" s="3"/>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3"/>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3652,60 +3822,66 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-      <c r="S71" s="3"/>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3"/>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>975900</v>
+      </c>
+      <c r="E72" s="3">
         <v>976000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>866500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>725700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>327900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>82900</v>
       </c>
-      <c r="I72" s="3">
-        <v>0</v>
-      </c>
       <c r="J72" s="3">
+        <v>0</v>
+      </c>
+      <c r="K72" s="3">
         <v>-58200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>22500</v>
-      </c>
-      <c r="L72" s="3">
-        <v>85600</v>
       </c>
       <c r="M72" s="3">
         <v>85600</v>
       </c>
       <c r="N72" s="3">
+        <v>85600</v>
+      </c>
+      <c r="O72" s="3">
         <v>83900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>94300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>106200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>116700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>137500</v>
       </c>
-      <c r="S72" s="3"/>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3"/>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3754,9 +3930,12 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-      <c r="S73" s="3"/>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3"/>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3805,9 +3984,12 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-      <c r="S74" s="3"/>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3"/>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3856,60 +4038,66 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-      <c r="S75" s="3"/>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3"/>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1572900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1544400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1422400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1233000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>825100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>568600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>474300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>412000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>153300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>25100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>33800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>45700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>56200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>77000</v>
       </c>
-      <c r="S76" s="3"/>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3"/>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3958,116 +4146,125 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-      <c r="S77" s="3"/>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3"/>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44653</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44289</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43918</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43554</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42886</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42521</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42155</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41790</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41425</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>41060</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>40694</v>
       </c>
-      <c r="S80" s="2"/>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2"/>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>206900</v>
+      </c>
+      <c r="E81" s="3">
         <v>198400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>146700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>401800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>248000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>84900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>58200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-58200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>15800</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
       <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>1700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-11900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-19400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-26600</v>
       </c>
-      <c r="S81" s="3"/>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3"/>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4087,59 +4284,63 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E83" s="3">
         <v>30300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>24100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>12100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3">
         <v>2000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2700</v>
       </c>
-      <c r="S83" s="3"/>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3"/>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4188,9 +4389,12 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-      <c r="S84" s="3"/>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3"/>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4239,9 +4443,12 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-      <c r="S85" s="3"/>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3"/>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4290,9 +4497,12 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-      <c r="S86" s="3"/>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3"/>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4341,9 +4551,12 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-      <c r="S87" s="3"/>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3"/>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4392,60 +4605,66 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-      <c r="S88" s="3"/>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3"/>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>303900</v>
+      </c>
+      <c r="E89" s="3">
         <v>240900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>222700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>416200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>224500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>153900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>76700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>65200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>31600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-17600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-18600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-25600</v>
       </c>
-      <c r="S89" s="3"/>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3"/>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4465,59 +4684,63 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-50500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-52900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-52200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-32000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-800</v>
       </c>
-      <c r="S91" s="3"/>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3"/>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4566,9 +4789,12 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-      <c r="S92" s="3"/>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3"/>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4617,60 +4843,66 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-      <c r="S93" s="3"/>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3"/>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-57200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-46200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-485700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-61200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-32000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-56800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>5600</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3">
         <v>13900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>22400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>32100</v>
       </c>
-      <c r="S94" s="3"/>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3"/>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4690,8 +4922,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4735,14 +4968,17 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-1500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-6000</v>
       </c>
-      <c r="S96" s="3"/>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3"/>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4791,9 +5027,12 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-      <c r="S97" s="3"/>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3"/>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4842,9 +5081,12 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-      <c r="S98" s="3"/>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3"/>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4893,90 +5135,96 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-      <c r="S99" s="3"/>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3"/>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-222200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-73000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>10900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-37000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-19900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-47800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>21600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-72500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>10300</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-2300</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-1500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6000</v>
       </c>
-      <c r="S100" s="3"/>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3"/>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
@@ -4989,64 +5237,70 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
-      <c r="S101" s="3"/>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3"/>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E102" s="3">
         <v>115300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-252400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>312000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>172800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>53100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>82800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>33900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>500</v>
       </c>
-      <c r="S102" s="3"/>
+      <c r="T102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
